--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -2324,7 +2324,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -5661,7 +5661,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -8070,7 +8070,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -9211,7 +9211,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="N124" t="n">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -9282,7 +9282,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="N125" t="n">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -5736,7 +5736,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="N75" t="n">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -5806,7 +5806,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="N76" t="n">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -5876,7 +5876,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="N77" t="n">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -5946,7 +5946,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="N78" t="n">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -7081,7 +7081,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="N94" t="n">

--- a/rules_backup.xlsx
+++ b/rules_backup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9363,6 +9363,78 @@
         <v>3</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>M10-Rule-1 Childhood Diseases Reported (Diphtheria, Pertussis, Neonatorum, Paralysis (AFP), Measles) (10.1.4+10.1.5+10.1.6+10.1.8+10.1.9 is not equal to 0)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>All Formats</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[10.1.4. :: Childhood Diseases - Diphtheria] +[10.1.5. :: Childhood Diseases - Pertussis] +[10.1.6. :: Childhood Diseases - Tetanus Neonatorum] +[10.1.8. :: Childhood Diseases - Acute Flaccid Paralysis(AFP)] +[10.1.9. :: Childhood Diseases - Measles] [10.1.9. :: Childhood Diseases - Measles] 
+</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>!=</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I127" t="b">
+        <v>1</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Single Month</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
